--- a/access_matrix.xlsx
+++ b/access_matrix.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -432,135 +432,215 @@
           <t>Access Role</t>
         </is>
       </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Target Synonym List (For Search Testing)</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Description / Sample Content</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>IT Engineer Onboarding Protocol</t>
+          <t>Poor Payment History Customer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>it</t>
+          <t>sales</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>it_staff</t>
+          <t>public</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>["bad credit", "poor payment history", "delayed payment"]</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Handling rules for customers with poor credit history.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>HR Onboarding Handbook</t>
+          <t>VIP Customer Privileges</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>hr</t>
+          <t>sales</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>hr_manager</t>
+          <t>public</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>["vip discount", "vip privileges", "loyalty program"]</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>VIP customer seating and discount rules.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Network Security &amp; System Firewall Policy</t>
+          <t>POS Pricing Fixes</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>it</t>
+          <t>sales</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>it_staff</t>
+          <t>public</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>["pos override", "pricing error", "incorrect price"]</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>POS manual price override and error handling.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Acceptable Hardware Use Agreement</t>
+          <t>Recommended Time for Purchasing</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ops</t>
+          <t>purchase</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
           <t>public</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>["inventory purchase time", "procurement timing", "stock refill"]</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Best procurement window at start of month.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Quy trình Bàn giao Công việc khi Nghỉ việc</t>
+          <t>Avoid Purchasing at Unusually Low Prices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>hr</t>
+          <t>purchase</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>hr_manager</t>
+          <t>public</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>["cheap stock warning", "unusually low prices", "supplier check"]</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Quality risk management for cheap ingredients.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Quy trình Vận hành Máy chủ và Backup</t>
+          <t>Preventing Missing or Incorrect Item Deliveries</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ops</t>
+          <t>helpdesk</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
           <t>public</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>["prevent delivery errors", "incorrect order", "missing items"]</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Verification checklists for order bags and drivers.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Troubleshooting</t>
+          <t>Customer Complaint Handling</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ops</t>
+          <t>foh</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
           <t>public</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>["customer complaints", "handling complaints", "refund rules"]</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Active listening, resolution, and escalation path.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Customer Complaint Handling</t>
+          <t>POS System Troubleshooting Guide</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>sales</t>
+          <t>technical</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -568,21 +648,14 @@
           <t>public</t>
         </is>
       </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>VIP Customer Privileges</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>sales</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>public</t>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>["pos frozen", "reboot cash register", "it support pos"]</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Check cables, soft reboot, switch to manual books.</t>
         </is>
       </c>
     </row>
